--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.7-threat-intelligence/WKBK/90_workbooks/ISMS-IMP-A.5.7.1_Sources_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.7-threat-intelligence/WKBK/90_workbooks/ISMS-IMP-A.5.7.1_Sources_Assessment_20260208.xlsx
@@ -26074,7 +26074,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08.02.2026 11:49:13</t>
+          <t>08.02.2026 12:25:41</t>
         </is>
       </c>
     </row>
